--- a/School_Mang/EXCEL/Final/Term_B/Term_B_3.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_3.xlsx
@@ -206,7 +206,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
@@ -311,28 +311,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF8B8B"/>
-          <bgColor rgb="FFFADF53"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC5C5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -670,7 +648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q152"/>
+  <dimension ref="A2:AD152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="8"/>
@@ -681,7 +659,7 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B2" s="14" t="s">
         <v>10</v>
       </c>
@@ -701,7 +679,7 @@
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="2"/>
@@ -720,7 +698,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -773,7 +751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="5"/>
@@ -816,7 +794,7 @@
       </c>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="5"/>
@@ -859,7 +837,7 @@
       </c>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="5"/>
@@ -902,7 +880,7 @@
       </c>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="5"/>
@@ -944,8 +922,12 @@
         <v>0</v>
       </c>
       <c r="Q8" s="11"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="AD8" s="1">
+        <f>SUM(E5:P20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="5"/>
@@ -988,7 +970,7 @@
       </c>
       <c r="Q9" s="12"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="5"/>
@@ -1031,7 +1013,7 @@
       </c>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="5"/>
@@ -1074,7 +1056,7 @@
       </c>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="5"/>
@@ -1117,7 +1099,7 @@
       </c>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="5"/>
@@ -1160,7 +1142,7 @@
       </c>
       <c r="Q13" s="12"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="5"/>
@@ -1203,7 +1185,7 @@
       </c>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="5"/>
@@ -1246,7 +1228,7 @@
       </c>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="5"/>
@@ -7159,7 +7141,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I152 N5:N152">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
-      <formula>4</formula>
+      <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:P152">
@@ -7167,9 +7149,9 @@
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H152 M5:N152">
+  <conditionalFormatting sqref="H5:H152 M5:M152">
     <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
-      <formula>16</formula>
+      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/School_Mang/EXCEL/Final/Term_B/Term_B_3.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_3.xlsx
@@ -206,50 +206,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF8B8B"/>
-          <bgColor rgb="FFFADF53"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC5C5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -7135,22 +7092,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:G152 J5:L152">
-    <cfRule type="cellIs" dxfId="9" priority="23" operator="greaterThan">
-      <formula>20</formula>
+    <cfRule type="cellIs" dxfId="6" priority="23" operator="greaterThan">
+      <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I152 N5:N152">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:P152">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H152 M5:M152">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
